--- a/employee_surveys/044_employee_performance_assessment_form--employee_surveys.xlsx
+++ b/employee_surveys/044_employee_performance_assessment_form--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,12 +707,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'teamwork'}</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Teamwork'}</t>
+          <t>Teamwork</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'problem_solving'}</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Problem solving'}</t>
+          <t>Problem solving</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Leadership'}</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'adaptability'}</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Adaptability'}</t>
+          <t>Adaptability</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'time_management'}</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Time management'}</t>
+          <t>Time management</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Leadership'}</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'time_management'}</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Time management'}</t>
+          <t>Time management</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'teamwork'}</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Teamwork'}</t>
+          <t>Teamwork</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'adaptability'}</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Adaptability'}</t>
+          <t>Adaptability</t>
         </is>
       </c>
     </row>
@@ -927,46 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'problem_solving'}</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'Problem solving'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>employee_skills_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'id':_7,_'name':_'time_management'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'id': 7, 'name': 'Time management'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>employee_skills_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'id':_8,_'name':_'leadership'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'id': 8, 'name': 'Leadership'}</t>
+          <t>Problem solving</t>
         </is>
       </c>
     </row>
